--- a/Team-Data/2008-09/11-10-2008-09.xlsx
+++ b/Team-Data/2008-09/11-10-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,10 +806,10 @@
         <v>10.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF2" t="n">
         <v>1</v>
@@ -754,10 +821,10 @@
         <v>11</v>
       </c>
       <c r="AI2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AJ2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK2" t="n">
         <v>17</v>
@@ -766,7 +833,7 @@
         <v>3</v>
       </c>
       <c r="AM2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN2" t="n">
         <v>7</v>
@@ -778,13 +845,13 @@
         <v>29</v>
       </c>
       <c r="AQ2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AR2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS2" t="n">
         <v>7</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>6</v>
       </c>
       <c r="AT2" t="n">
         <v>5</v>
@@ -793,25 +860,25 @@
         <v>12</v>
       </c>
       <c r="AV2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AW2" t="n">
         <v>8</v>
       </c>
       <c r="AX2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AY2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BC2" t="n">
         <v>2</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>11-10-2008-09</t>
+          <t>2008-11-10</t>
         </is>
       </c>
     </row>
@@ -858,70 +925,70 @@
         <v>48</v>
       </c>
       <c r="I3" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="L3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="M3" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="O3" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="P3" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.712</v>
+      </c>
+      <c r="R3" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="S3" t="n">
         <v>34</v>
       </c>
-      <c r="J3" t="n">
-        <v>76.7</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.443</v>
-      </c>
-      <c r="L3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="M3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.294</v>
-      </c>
-      <c r="O3" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="P3" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="R3" t="n">
-        <v>11</v>
-      </c>
-      <c r="S3" t="n">
-        <v>35.1</v>
-      </c>
       <c r="T3" t="n">
-        <v>46.1</v>
+        <v>45.7</v>
       </c>
       <c r="U3" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="V3" t="n">
-        <v>17.7</v>
+        <v>18.6</v>
       </c>
       <c r="W3" t="n">
-        <v>8.9</v>
+        <v>9.6</v>
       </c>
       <c r="X3" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="Y3" t="n">
         <v>4.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA3" t="n">
-        <v>25.1</v>
+        <v>25.6</v>
       </c>
       <c r="AB3" t="n">
-        <v>93.90000000000001</v>
+        <v>93.3</v>
       </c>
       <c r="AC3" t="n">
-        <v>6.9</v>
+        <v>6.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -936,64 +1003,64 @@
         <v>11</v>
       </c>
       <c r="AI3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>28</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>26</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ3" t="n">
         <v>24</v>
       </c>
-      <c r="AJ3" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>18</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>26</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>26</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>20</v>
-      </c>
       <c r="AR3" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AS3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT3" t="n">
         <v>4</v>
       </c>
       <c r="AU3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AV3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AW3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AX3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AY3" t="n">
         <v>11</v>
       </c>
       <c r="AZ3" t="n">
+        <v>27</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB3" t="n">
         <v>25</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>23</v>
       </c>
       <c r="BC3" t="n">
         <v>5</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>11-10-2008-09</t>
+          <t>2008-11-10</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-5.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE4" t="n">
         <v>20</v>
@@ -1112,7 +1179,7 @@
         <v>18</v>
       </c>
       <c r="AG4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AH4" t="n">
         <v>11</v>
@@ -1133,16 +1200,16 @@
         <v>28</v>
       </c>
       <c r="AN4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AO4" t="n">
         <v>8</v>
       </c>
       <c r="AP4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR4" t="n">
         <v>10</v>
@@ -1157,7 +1224,7 @@
         <v>27</v>
       </c>
       <c r="AV4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AW4" t="n">
         <v>17</v>
@@ -1169,10 +1236,10 @@
         <v>26</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB4" t="n">
         <v>28</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>11-10-2008-09</t>
+          <t>2008-11-10</t>
         </is>
       </c>
     </row>
@@ -1207,160 +1274,160 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>0.333</v>
+        <v>0.429</v>
       </c>
       <c r="H5" t="n">
         <v>48</v>
       </c>
       <c r="I5" t="n">
-        <v>33.7</v>
+        <v>33.9</v>
       </c>
       <c r="J5" t="n">
-        <v>82.5</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>0.408</v>
+        <v>0.42</v>
       </c>
       <c r="L5" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="M5" t="n">
-        <v>15</v>
+        <v>14.6</v>
       </c>
       <c r="N5" t="n">
-        <v>0.378</v>
+        <v>0.382</v>
       </c>
       <c r="O5" t="n">
-        <v>20.2</v>
+        <v>22</v>
       </c>
       <c r="P5" t="n">
-        <v>25.3</v>
+        <v>28</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.796</v>
+        <v>0.786</v>
       </c>
       <c r="R5" t="n">
-        <v>12.8</v>
+        <v>13</v>
       </c>
       <c r="S5" t="n">
-        <v>30.7</v>
+        <v>30</v>
       </c>
       <c r="T5" t="n">
-        <v>43.5</v>
+        <v>43</v>
       </c>
       <c r="U5" t="n">
-        <v>17.2</v>
+        <v>18.6</v>
       </c>
       <c r="V5" t="n">
-        <v>15.3</v>
+        <v>15.9</v>
       </c>
       <c r="W5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X5" t="n">
         <v>6.3</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="Z5" t="n">
-        <v>23.2</v>
+        <v>22.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.8</v>
+        <v>23</v>
       </c>
       <c r="AB5" t="n">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2.5</v>
+        <v>-0.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AE5" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AF5" t="n">
         <v>18</v>
       </c>
       <c r="AG5" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AH5" t="n">
         <v>11</v>
       </c>
       <c r="AI5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ5" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AK5" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AL5" t="n">
         <v>17</v>
       </c>
       <c r="AM5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN5" t="n">
         <v>10</v>
       </c>
       <c r="AO5" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AP5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AQ5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR5" t="n">
         <v>6</v>
       </c>
       <c r="AS5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AT5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW5" t="n">
         <v>9</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>28</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>19</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>10</v>
       </c>
       <c r="AX5" t="n">
         <v>4</v>
       </c>
       <c r="AY5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB5" t="n">
         <v>22</v>
       </c>
-      <c r="AZ5" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>15</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>25</v>
-      </c>
       <c r="BC5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>11-10-2008-09</t>
+          <t>2008-11-10</t>
         </is>
       </c>
     </row>
@@ -1389,160 +1456,160 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
         <v>5</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>0.833</v>
+        <v>0.714</v>
       </c>
       <c r="H6" t="n">
         <v>48</v>
       </c>
       <c r="I6" t="n">
-        <v>36.8</v>
+        <v>35.7</v>
       </c>
       <c r="J6" t="n">
-        <v>77.8</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>0.473</v>
+        <v>0.467</v>
       </c>
       <c r="L6" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="M6" t="n">
-        <v>18.2</v>
+        <v>17.7</v>
       </c>
       <c r="N6" t="n">
-        <v>0.358</v>
+        <v>0.339</v>
       </c>
       <c r="O6" t="n">
-        <v>21.8</v>
+        <v>22.1</v>
       </c>
       <c r="P6" t="n">
-        <v>28.2</v>
+        <v>28.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.775</v>
+        <v>0.767</v>
       </c>
       <c r="R6" t="n">
-        <v>11.3</v>
+        <v>10.9</v>
       </c>
       <c r="S6" t="n">
-        <v>29.7</v>
+        <v>30.1</v>
       </c>
       <c r="T6" t="n">
         <v>41</v>
       </c>
       <c r="U6" t="n">
-        <v>20</v>
+        <v>19.4</v>
       </c>
       <c r="V6" t="n">
-        <v>14.2</v>
+        <v>15.3</v>
       </c>
       <c r="W6" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="X6" t="n">
-        <v>6.8</v>
+        <v>6.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="Z6" t="n">
-        <v>21.5</v>
+        <v>22.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>21.7</v>
+        <v>22.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>102</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.5</v>
+        <v>6.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AE6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AG6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH6" t="n">
         <v>11</v>
       </c>
       <c r="AI6" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AJ6" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AK6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AL6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AM6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AN6" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AO6" t="n">
         <v>4</v>
       </c>
       <c r="AP6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AQ6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR6" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AS6" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="AT6" t="n">
         <v>18</v>
       </c>
       <c r="AU6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AV6" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="AW6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA6" t="n">
         <v>13</v>
       </c>
-      <c r="AX6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY6" t="n">
+      <c r="BB6" t="n">
         <v>8</v>
       </c>
-      <c r="AZ6" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>17</v>
-      </c>
-      <c r="BB6" t="n">
+      <c r="BC6" t="n">
         <v>5</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>3</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>11-10-2008-09</t>
+          <t>2008-11-10</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>-2.7</v>
       </c>
       <c r="AD7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE7" t="n">
         <v>20</v>
@@ -1658,31 +1725,31 @@
         <v>18</v>
       </c>
       <c r="AG7" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AH7" t="n">
         <v>11</v>
       </c>
       <c r="AI7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AJ7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK7" t="n">
         <v>20</v>
       </c>
       <c r="AL7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AN7" t="n">
         <v>25</v>
       </c>
       <c r="AO7" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AP7" t="n">
         <v>28</v>
@@ -1691,19 +1758,19 @@
         <v>5</v>
       </c>
       <c r="AR7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AT7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU7" t="n">
         <v>13</v>
       </c>
       <c r="AV7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW7" t="n">
         <v>17</v>
@@ -1715,13 +1782,13 @@
         <v>8</v>
       </c>
       <c r="AZ7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC7" t="n">
         <v>20</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>11-10-2008-09</t>
+          <t>2008-11-10</t>
         </is>
       </c>
     </row>
@@ -1831,16 +1898,16 @@
         <v>0.3</v>
       </c>
       <c r="AD8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF8" t="n">
         <v>12</v>
       </c>
-      <c r="AE8" t="n">
-        <v>15</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>11</v>
-      </c>
       <c r="AG8" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AH8" t="n">
         <v>4</v>
@@ -1849,13 +1916,13 @@
         <v>18</v>
       </c>
       <c r="AJ8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AK8" t="n">
         <v>19</v>
       </c>
       <c r="AL8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM8" t="n">
         <v>20</v>
@@ -1867,10 +1934,10 @@
         <v>1</v>
       </c>
       <c r="AP8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AR8" t="n">
         <v>22</v>
@@ -1882,16 +1949,16 @@
         <v>3</v>
       </c>
       <c r="AU8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV8" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AW8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY8" t="n">
         <v>30</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>11-10-2008-09</t>
+          <t>2008-11-10</t>
         </is>
       </c>
     </row>
@@ -2013,13 +2080,13 @@
         <v>3.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG9" t="n">
         <v>7</v>
@@ -2031,46 +2098,46 @@
         <v>16</v>
       </c>
       <c r="AJ9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AK9" t="n">
         <v>16</v>
       </c>
       <c r="AL9" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AM9" t="n">
         <v>18</v>
       </c>
       <c r="AN9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ9" t="n">
         <v>7</v>
       </c>
       <c r="AR9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AS9" t="n">
         <v>21</v>
       </c>
       <c r="AT9" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AU9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV9" t="n">
         <v>6</v>
       </c>
       <c r="AW9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX9" t="n">
         <v>9</v>
@@ -2079,16 +2146,16 @@
         <v>6</v>
       </c>
       <c r="AZ9" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BA9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB9" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BC9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>11-10-2008-09</t>
+          <t>2008-11-10</t>
         </is>
       </c>
     </row>
@@ -2195,13 +2262,13 @@
         <v>-3.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE10" t="n">
         <v>20</v>
       </c>
       <c r="AF10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG10" t="n">
         <v>25</v>
@@ -2210,7 +2277,7 @@
         <v>10</v>
       </c>
       <c r="AI10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ10" t="n">
         <v>1</v>
@@ -2228,7 +2295,7 @@
         <v>28</v>
       </c>
       <c r="AO10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP10" t="n">
         <v>3</v>
@@ -2240,22 +2307,22 @@
         <v>2</v>
       </c>
       <c r="AS10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW10" t="n">
         <v>9</v>
       </c>
       <c r="AX10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY10" t="n">
         <v>27</v>
@@ -2267,10 +2334,10 @@
         <v>1</v>
       </c>
       <c r="BB10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BC10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>11-10-2008-09</t>
+          <t>2008-11-10</t>
         </is>
       </c>
     </row>
@@ -2377,43 +2444,43 @@
         <v>1</v>
       </c>
       <c r="AD11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH11" t="n">
         <v>7</v>
       </c>
       <c r="AI11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ11" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AK11" t="n">
         <v>27</v>
       </c>
       <c r="AL11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP11" t="n">
         <v>15</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>15</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>5</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>14</v>
       </c>
       <c r="AQ11" t="n">
         <v>1</v>
@@ -2422,19 +2489,19 @@
         <v>19</v>
       </c>
       <c r="AS11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT11" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AU11" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AV11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AW11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX11" t="n">
         <v>28</v>
@@ -2443,10 +2510,10 @@
         <v>28</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB11" t="n">
         <v>24</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>11-10-2008-09</t>
+          <t>2008-11-10</t>
         </is>
       </c>
     </row>
@@ -2481,160 +2548,160 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F12" t="n">
         <v>3</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H12" t="n">
         <v>48</v>
       </c>
       <c r="I12" t="n">
-        <v>37.2</v>
+        <v>36.4</v>
       </c>
       <c r="J12" t="n">
-        <v>81.3</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>0.457</v>
+        <v>0.452</v>
       </c>
       <c r="L12" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
       <c r="M12" t="n">
-        <v>21.8</v>
+        <v>23.4</v>
       </c>
       <c r="N12" t="n">
-        <v>0.336</v>
+        <v>0.342</v>
       </c>
       <c r="O12" t="n">
-        <v>19</v>
+        <v>18.6</v>
       </c>
       <c r="P12" t="n">
-        <v>24.2</v>
+        <v>23.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.786</v>
+        <v>0.802</v>
       </c>
       <c r="R12" t="n">
-        <v>11.2</v>
+        <v>11.8</v>
       </c>
       <c r="S12" t="n">
-        <v>31.8</v>
+        <v>31.6</v>
       </c>
       <c r="T12" t="n">
-        <v>43</v>
+        <v>43.4</v>
       </c>
       <c r="U12" t="n">
         <v>21</v>
       </c>
       <c r="V12" t="n">
-        <v>16.5</v>
+        <v>17.6</v>
       </c>
       <c r="W12" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="X12" t="n">
-        <v>6.3</v>
+        <v>5.6</v>
       </c>
       <c r="Y12" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="Z12" t="n">
-        <v>23.2</v>
+        <v>23.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>22.3</v>
+        <v>22</v>
       </c>
       <c r="AB12" t="n">
-        <v>100.7</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="AD12" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF12" t="n">
         <v>12</v>
       </c>
-      <c r="AE12" t="n">
-        <v>15</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>11</v>
-      </c>
       <c r="AG12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AH12" t="n">
         <v>11</v>
       </c>
       <c r="AI12" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AJ12" t="n">
         <v>14</v>
       </c>
       <c r="AK12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS12" t="n">
         <v>8</v>
       </c>
-      <c r="AL12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>19</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>20</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>20</v>
-      </c>
-      <c r="AQ12" t="n">
+      <c r="AT12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU12" t="n">
         <v>10</v>
       </c>
-      <c r="AR12" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT12" t="n">
+      <c r="AV12" t="n">
+        <v>28</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX12" t="n">
         <v>11</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>11</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>22</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>11</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>4</v>
       </c>
       <c r="AY12" t="n">
         <v>29</v>
       </c>
       <c r="AZ12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BA12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BB12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BC12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>11-10-2008-09</t>
+          <t>2008-11-10</t>
         </is>
       </c>
     </row>
@@ -2741,16 +2808,16 @@
         <v>-14.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE13" t="n">
         <v>26</v>
       </c>
       <c r="AF13" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG13" t="n">
         <v>29</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>28</v>
       </c>
       <c r="AH13" t="n">
         <v>7</v>
@@ -2759,7 +2826,7 @@
         <v>26</v>
       </c>
       <c r="AJ13" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AK13" t="n">
         <v>28</v>
@@ -2768,7 +2835,7 @@
         <v>19</v>
       </c>
       <c r="AM13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AN13" t="n">
         <v>23</v>
@@ -2777,7 +2844,7 @@
         <v>28</v>
       </c>
       <c r="AP13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AQ13" t="n">
         <v>27</v>
@@ -2786,34 +2853,34 @@
         <v>18</v>
       </c>
       <c r="AS13" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AT13" t="n">
         <v>17</v>
       </c>
       <c r="AU13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW13" t="n">
         <v>22</v>
       </c>
       <c r="AX13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY13" t="n">
         <v>18</v>
       </c>
       <c r="AZ13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BA13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB13" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BC13" t="n">
         <v>30</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>11-10-2008-09</t>
+          <t>2008-11-10</t>
         </is>
       </c>
     </row>
@@ -2845,10 +2912,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -2860,73 +2927,73 @@
         <v>48</v>
       </c>
       <c r="I14" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="J14" t="n">
-        <v>82.8</v>
+        <v>82</v>
       </c>
       <c r="K14" t="n">
-        <v>0.45</v>
+        <v>0.454</v>
       </c>
       <c r="L14" t="n">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="M14" t="n">
-        <v>18.8</v>
+        <v>17</v>
       </c>
       <c r="N14" t="n">
-        <v>0.44</v>
+        <v>0.471</v>
       </c>
       <c r="O14" t="n">
-        <v>26.8</v>
+        <v>24.4</v>
       </c>
       <c r="P14" t="n">
-        <v>36</v>
+        <v>32.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.743</v>
+        <v>0.753</v>
       </c>
       <c r="R14" t="n">
-        <v>14.5</v>
+        <v>13.4</v>
       </c>
       <c r="S14" t="n">
-        <v>37.5</v>
+        <v>38</v>
       </c>
       <c r="T14" t="n">
-        <v>52</v>
+        <v>51.4</v>
       </c>
       <c r="U14" t="n">
-        <v>21.5</v>
+        <v>21</v>
       </c>
       <c r="V14" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="W14" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="X14" t="n">
         <v>6.8</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="Z14" t="n">
-        <v>20</v>
+        <v>19.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>25.5</v>
+        <v>23.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>109.5</v>
+        <v>106.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>23</v>
+        <v>22.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AE14" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AF14" t="n">
         <v>1</v>
@@ -2944,28 +3011,28 @@
         <v>8</v>
       </c>
       <c r="AK14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AL14" t="n">
         <v>4</v>
       </c>
       <c r="AM14" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AN14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO14" t="n">
         <v>2</v>
       </c>
       <c r="AP14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AR14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS14" t="n">
         <v>1</v>
@@ -2974,25 +3041,25 @@
         <v>1</v>
       </c>
       <c r="AU14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AV14" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX14" t="n">
         <v>3</v>
       </c>
       <c r="AY14" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AZ14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB14" t="n">
         <v>1</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>11-10-2008-09</t>
+          <t>2008-11-10</t>
         </is>
       </c>
     </row>
@@ -3027,160 +3094,160 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E15" t="n">
         <v>3</v>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G15" t="n">
-        <v>0.375</v>
+        <v>0.429</v>
       </c>
       <c r="H15" t="n">
         <v>48</v>
       </c>
       <c r="I15" t="n">
-        <v>33.3</v>
+        <v>32.6</v>
       </c>
       <c r="J15" t="n">
-        <v>78.40000000000001</v>
+        <v>77.3</v>
       </c>
       <c r="K15" t="n">
-        <v>0.424</v>
+        <v>0.421</v>
       </c>
       <c r="L15" t="n">
         <v>4.3</v>
       </c>
       <c r="M15" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="N15" t="n">
-        <v>0.304</v>
+        <v>0.309</v>
       </c>
       <c r="O15" t="n">
-        <v>20.4</v>
+        <v>20.1</v>
       </c>
       <c r="P15" t="n">
-        <v>26.9</v>
+        <v>27.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.758</v>
+        <v>0.742</v>
       </c>
       <c r="R15" t="n">
         <v>11.3</v>
       </c>
       <c r="S15" t="n">
-        <v>32.1</v>
+        <v>32.7</v>
       </c>
       <c r="T15" t="n">
-        <v>43.4</v>
+        <v>44</v>
       </c>
       <c r="U15" t="n">
-        <v>15.5</v>
+        <v>16.3</v>
       </c>
       <c r="V15" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="W15" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="X15" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Y15" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Z15" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="AA15" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="AB15" t="n">
-        <v>91.09999999999999</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="AC15" t="n">
-        <v>-2.9</v>
+        <v>-2.6</v>
       </c>
       <c r="AD15" t="n">
         <v>1</v>
       </c>
       <c r="AE15" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AF15" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AG15" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AH15" t="n">
         <v>11</v>
       </c>
       <c r="AI15" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AJ15" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AK15" t="n">
         <v>24</v>
       </c>
       <c r="AL15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AN15" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AO15" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AP15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ15" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AR15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS15" t="n">
         <v>5</v>
       </c>
       <c r="AT15" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AU15" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AV15" t="n">
         <v>22</v>
       </c>
       <c r="AW15" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AX15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ15" t="n">
         <v>24</v>
       </c>
       <c r="BA15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB15" t="n">
         <v>27</v>
       </c>
       <c r="BC15" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>11-10-2008-09</t>
+          <t>2008-11-10</t>
         </is>
       </c>
     </row>
@@ -3209,136 +3276,136 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F16" t="n">
         <v>3</v>
       </c>
       <c r="G16" t="n">
-        <v>0.571</v>
+        <v>0.5</v>
       </c>
       <c r="H16" t="n">
         <v>48</v>
       </c>
       <c r="I16" t="n">
-        <v>35.6</v>
+        <v>36.3</v>
       </c>
       <c r="J16" t="n">
-        <v>78.09999999999999</v>
+        <v>79.5</v>
       </c>
       <c r="K16" t="n">
-        <v>0.455</v>
+        <v>0.457</v>
       </c>
       <c r="L16" t="n">
-        <v>7.3</v>
+        <v>6.7</v>
       </c>
       <c r="M16" t="n">
-        <v>20.4</v>
+        <v>19.7</v>
       </c>
       <c r="N16" t="n">
-        <v>0.357</v>
+        <v>0.339</v>
       </c>
       <c r="O16" t="n">
-        <v>21.3</v>
+        <v>20.5</v>
       </c>
       <c r="P16" t="n">
-        <v>28.6</v>
+        <v>28</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.745</v>
+        <v>0.732</v>
       </c>
       <c r="R16" t="n">
-        <v>10.4</v>
+        <v>10.7</v>
       </c>
       <c r="S16" t="n">
-        <v>28.1</v>
+        <v>29.2</v>
       </c>
       <c r="T16" t="n">
-        <v>38.6</v>
+        <v>39.8</v>
       </c>
       <c r="U16" t="n">
-        <v>19.9</v>
+        <v>20.7</v>
       </c>
       <c r="V16" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="W16" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="X16" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF16" t="n">
         <v>12</v>
       </c>
-      <c r="W16" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="X16" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>99.7</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>6</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>11</v>
-      </c>
       <c r="AG16" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AH16" t="n">
         <v>11</v>
       </c>
       <c r="AI16" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AJ16" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AK16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL16" t="n">
         <v>9</v>
       </c>
       <c r="AM16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AN16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP16" t="n">
         <v>9</v>
       </c>
-      <c r="AP16" t="n">
-        <v>8</v>
-      </c>
       <c r="AQ16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR16" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AS16" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AT16" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AU16" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AV16" t="n">
         <v>3</v>
@@ -3347,22 +3414,22 @@
         <v>1</v>
       </c>
       <c r="AX16" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AY16" t="n">
         <v>2</v>
       </c>
       <c r="AZ16" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB16" t="n">
         <v>7</v>
       </c>
-      <c r="BA16" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>9</v>
-      </c>
       <c r="BC16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>11-10-2008-09</t>
+          <t>2008-11-10</t>
         </is>
       </c>
     </row>
@@ -3391,160 +3458,160 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17" t="n">
         <v>3</v>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5</v>
+        <v>0.429</v>
       </c>
       <c r="H17" t="n">
-        <v>48.8</v>
+        <v>48.7</v>
       </c>
       <c r="I17" t="n">
         <v>36.7</v>
       </c>
       <c r="J17" t="n">
-        <v>82.2</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.446</v>
+        <v>0.45</v>
       </c>
       <c r="L17" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="M17" t="n">
         <v>13.7</v>
       </c>
       <c r="N17" t="n">
-        <v>0.366</v>
+        <v>0.375</v>
       </c>
       <c r="O17" t="n">
-        <v>17.7</v>
+        <v>17.3</v>
       </c>
       <c r="P17" t="n">
-        <v>25.2</v>
+        <v>24.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.702</v>
+        <v>0.708</v>
       </c>
       <c r="R17" t="n">
-        <v>11.3</v>
+        <v>11.6</v>
       </c>
       <c r="S17" t="n">
-        <v>31.7</v>
+        <v>29.9</v>
       </c>
       <c r="T17" t="n">
-        <v>43</v>
+        <v>41.4</v>
       </c>
       <c r="U17" t="n">
-        <v>23</v>
+        <v>22.7</v>
       </c>
       <c r="V17" t="n">
-        <v>17</v>
+        <v>17.3</v>
       </c>
       <c r="W17" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="X17" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Y17" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="Z17" t="n">
-        <v>25.8</v>
+        <v>26.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>24.2</v>
+        <v>23.3</v>
       </c>
       <c r="AB17" t="n">
-        <v>96</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.5</v>
+        <v>-1.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AE17" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AF17" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="AG17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH17" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AI17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AJ17" t="n">
         <v>10</v>
       </c>
       <c r="AK17" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AL17" t="n">
         <v>21</v>
       </c>
       <c r="AM17" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AN17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AO17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP17" t="n">
+        <v>19</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>18</v>
+      </c>
+      <c r="AT17" t="n">
         <v>16</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>26</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>11</v>
       </c>
       <c r="AU17" t="n">
         <v>5</v>
       </c>
       <c r="AV17" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AW17" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AX17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AY17" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AZ17" t="n">
         <v>29</v>
       </c>
       <c r="BA17" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="BB17" t="n">
         <v>19</v>
       </c>
       <c r="BC17" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>11-10-2008-09</t>
+          <t>2008-11-10</t>
         </is>
       </c>
     </row>
@@ -3651,13 +3718,13 @@
         <v>-5.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE18" t="n">
         <v>26</v>
       </c>
       <c r="AF18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG18" t="n">
         <v>27</v>
@@ -3678,34 +3745,34 @@
         <v>23</v>
       </c>
       <c r="AM18" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AN18" t="n">
         <v>21</v>
       </c>
       <c r="AO18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AQ18" t="n">
         <v>4</v>
       </c>
       <c r="AR18" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AS18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AT18" t="n">
         <v>21</v>
       </c>
       <c r="AU18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW18" t="n">
         <v>27</v>
@@ -3717,16 +3784,16 @@
         <v>20</v>
       </c>
       <c r="AZ18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA18" t="n">
         <v>19</v>
       </c>
       <c r="BB18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>11-10-2008-09</t>
+          <t>2008-11-10</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E19" t="n">
         <v>2</v>
       </c>
       <c r="F19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>0.333</v>
+        <v>0.4</v>
       </c>
       <c r="H19" t="n">
         <v>48</v>
@@ -3773,73 +3840,73 @@
         <v>32.8</v>
       </c>
       <c r="J19" t="n">
-        <v>78.7</v>
+        <v>80.2</v>
       </c>
       <c r="K19" t="n">
-        <v>0.417</v>
+        <v>0.409</v>
       </c>
       <c r="L19" t="n">
-        <v>6.8</v>
+        <v>5.6</v>
       </c>
       <c r="M19" t="n">
-        <v>19.5</v>
+        <v>18.4</v>
       </c>
       <c r="N19" t="n">
-        <v>0.35</v>
+        <v>0.304</v>
       </c>
       <c r="O19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P19" t="n">
-        <v>25.7</v>
+        <v>26.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.779</v>
+        <v>0.784</v>
       </c>
       <c r="R19" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="S19" t="n">
-        <v>29.2</v>
+        <v>29.4</v>
       </c>
       <c r="T19" t="n">
-        <v>40.5</v>
+        <v>40.8</v>
       </c>
       <c r="U19" t="n">
-        <v>17.7</v>
+        <v>17.4</v>
       </c>
       <c r="V19" t="n">
-        <v>14.2</v>
+        <v>13.2</v>
       </c>
       <c r="W19" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="X19" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Y19" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="Z19" t="n">
-        <v>26.5</v>
+        <v>26.8</v>
       </c>
       <c r="AA19" t="n">
-        <v>20.5</v>
+        <v>21.2</v>
       </c>
       <c r="AB19" t="n">
-        <v>92.5</v>
+        <v>92.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>-7</v>
+        <v>-7.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="AE19" t="n">
         <v>20</v>
       </c>
       <c r="AF19" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AG19" t="n">
         <v>20</v>
@@ -3848,67 +3915,67 @@
         <v>11</v>
       </c>
       <c r="AI19" t="n">
+        <v>28</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK19" t="n">
         <v>29</v>
       </c>
-      <c r="AJ19" t="n">
-        <v>20</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>26</v>
-      </c>
       <c r="AL19" t="n">
+        <v>16</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO19" t="n">
         <v>10</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>8</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>18</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>15</v>
       </c>
       <c r="AP19" t="n">
         <v>13</v>
       </c>
       <c r="AQ19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AR19" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AS19" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AT19" t="n">
         <v>20</v>
       </c>
       <c r="AU19" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AV19" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AW19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX19" t="n">
         <v>13</v>
       </c>
       <c r="AY19" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AZ19" t="n">
         <v>30</v>
       </c>
       <c r="BA19" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BB19" t="n">
         <v>26</v>
       </c>
       <c r="BC19" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>11-10-2008-09</t>
+          <t>2008-11-10</t>
         </is>
       </c>
     </row>
@@ -4015,13 +4082,13 @@
         <v>5</v>
       </c>
       <c r="AD20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG20" t="n">
         <v>7</v>
@@ -4033,7 +4100,7 @@
         <v>21</v>
       </c>
       <c r="AJ20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK20" t="n">
         <v>7</v>
@@ -4048,28 +4115,28 @@
         <v>3</v>
       </c>
       <c r="AO20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AQ20" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AR20" t="n">
         <v>25</v>
       </c>
       <c r="AS20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AT20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AU20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW20" t="n">
         <v>7</v>
@@ -4081,16 +4148,16 @@
         <v>3</v>
       </c>
       <c r="AZ20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BB20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>11-10-2008-09</t>
+          <t>2008-11-10</t>
         </is>
       </c>
     </row>
@@ -4197,13 +4264,13 @@
         <v>-2.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG21" t="n">
         <v>7</v>
@@ -4230,13 +4297,13 @@
         <v>12</v>
       </c>
       <c r="AO21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AQ21" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AR21" t="n">
         <v>19</v>
@@ -4251,10 +4318,10 @@
         <v>4</v>
       </c>
       <c r="AV21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>11-10-2008-09</t>
+          <t>2008-11-10</t>
         </is>
       </c>
     </row>
@@ -4301,103 +4368,103 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G22" t="n">
-        <v>0.143</v>
+        <v>0.167</v>
       </c>
       <c r="H22" t="n">
         <v>48</v>
       </c>
       <c r="I22" t="n">
-        <v>34.1</v>
+        <v>33.8</v>
       </c>
       <c r="J22" t="n">
-        <v>84.40000000000001</v>
+        <v>83</v>
       </c>
       <c r="K22" t="n">
-        <v>0.404</v>
+        <v>0.408</v>
       </c>
       <c r="L22" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="M22" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="N22" t="n">
-        <v>0.377</v>
+        <v>0.357</v>
       </c>
       <c r="O22" t="n">
-        <v>16.9</v>
+        <v>16</v>
       </c>
       <c r="P22" t="n">
-        <v>22.6</v>
+        <v>22</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.747</v>
+        <v>0.727</v>
       </c>
       <c r="R22" t="n">
-        <v>13.3</v>
+        <v>12.3</v>
       </c>
       <c r="S22" t="n">
-        <v>30.3</v>
+        <v>30</v>
       </c>
       <c r="T22" t="n">
-        <v>43.6</v>
+        <v>42.3</v>
       </c>
       <c r="U22" t="n">
-        <v>16.3</v>
+        <v>15.8</v>
       </c>
       <c r="V22" t="n">
-        <v>16.1</v>
+        <v>15.8</v>
       </c>
       <c r="W22" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="X22" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y22" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="Z22" t="n">
-        <v>22.9</v>
+        <v>22.7</v>
       </c>
       <c r="AA22" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>88</v>
+        <v>86.2</v>
       </c>
       <c r="AC22" t="n">
-        <v>-7.4</v>
+        <v>-7.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="AE22" t="n">
         <v>26</v>
       </c>
       <c r="AF22" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AG22" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AH22" t="n">
         <v>11</v>
       </c>
       <c r="AI22" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AJ22" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AK22" t="n">
         <v>30</v>
@@ -4409,52 +4476,52 @@
         <v>30</v>
       </c>
       <c r="AN22" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AO22" t="n">
         <v>26</v>
       </c>
       <c r="AP22" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ22" t="n">
+        <v>23</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>30</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>18</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ22" t="n">
         <v>21</v>
       </c>
-      <c r="AR22" t="n">
-        <v>5</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>16</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>29</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>14</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>16</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>25</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>19</v>
-      </c>
       <c r="BA22" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>30</v>
+      </c>
+      <c r="BC22" t="n">
         <v>27</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>29</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>28</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>11-10-2008-09</t>
+          <t>2008-11-10</t>
         </is>
       </c>
     </row>
@@ -4483,130 +4550,130 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E23" t="n">
         <v>4</v>
       </c>
       <c r="F23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G23" t="n">
-        <v>0.571</v>
+        <v>0.667</v>
       </c>
       <c r="H23" t="n">
         <v>48</v>
       </c>
       <c r="I23" t="n">
-        <v>35.1</v>
+        <v>35.7</v>
       </c>
       <c r="J23" t="n">
-        <v>78.09999999999999</v>
+        <v>79.3</v>
       </c>
       <c r="K23" t="n">
         <v>0.45</v>
       </c>
       <c r="L23" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="M23" t="n">
-        <v>25.1</v>
+        <v>25.3</v>
       </c>
       <c r="N23" t="n">
-        <v>0.313</v>
+        <v>0.316</v>
       </c>
       <c r="O23" t="n">
-        <v>20.3</v>
+        <v>19</v>
       </c>
       <c r="P23" t="n">
-        <v>29.9</v>
+        <v>28.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.679</v>
+        <v>0.667</v>
       </c>
       <c r="R23" t="n">
-        <v>12.4</v>
+        <v>12.8</v>
       </c>
       <c r="S23" t="n">
-        <v>31.9</v>
+        <v>31.5</v>
       </c>
       <c r="T23" t="n">
         <v>44.3</v>
       </c>
       <c r="U23" t="n">
-        <v>17.7</v>
+        <v>18.2</v>
       </c>
       <c r="V23" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W23" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
       <c r="X23" t="n">
-        <v>6.3</v>
+        <v>7.2</v>
       </c>
       <c r="Y23" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="Z23" t="n">
-        <v>21</v>
+        <v>20.2</v>
       </c>
       <c r="AA23" t="n">
-        <v>23.9</v>
+        <v>23.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>98.40000000000001</v>
+        <v>98.3</v>
       </c>
       <c r="AC23" t="n">
-        <v>4.7</v>
+        <v>6.7</v>
       </c>
       <c r="AD23" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="AE23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF23" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AG23" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AH23" t="n">
         <v>11</v>
       </c>
       <c r="AI23" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AJ23" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AK23" t="n">
         <v>12</v>
       </c>
       <c r="AL23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AM23" t="n">
         <v>2</v>
       </c>
       <c r="AN23" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AO23" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="AP23" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AQ23" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AR23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AS23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AT23" t="n">
         <v>6</v>
@@ -4615,28 +4682,28 @@
         <v>25</v>
       </c>
       <c r="AV23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW23" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AX23" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AY23" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC23" t="n">
         <v>4</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>13</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>8</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>11-10-2008-09</t>
+          <t>2008-11-10</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>2</v>
       </c>
       <c r="AD24" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE24" t="n">
         <v>20</v>
@@ -4752,7 +4819,7 @@
         <v>18</v>
       </c>
       <c r="AG24" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AH24" t="n">
         <v>11</v>
@@ -4761,7 +4828,7 @@
         <v>4</v>
       </c>
       <c r="AJ24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK24" t="n">
         <v>14</v>
@@ -4770,25 +4837,25 @@
         <v>18</v>
       </c>
       <c r="AM24" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AN24" t="n">
         <v>9</v>
       </c>
       <c r="AO24" t="n">
+        <v>23</v>
+      </c>
+      <c r="AP24" t="n">
         <v>24</v>
       </c>
-      <c r="AP24" t="n">
-        <v>25</v>
-      </c>
       <c r="AQ24" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR24" t="n">
         <v>1</v>
       </c>
       <c r="AS24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT24" t="n">
         <v>2</v>
@@ -4797,7 +4864,7 @@
         <v>21</v>
       </c>
       <c r="AV24" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AW24" t="n">
         <v>27</v>
@@ -4809,13 +4876,13 @@
         <v>15</v>
       </c>
       <c r="AZ24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA24" t="n">
         <v>29</v>
       </c>
       <c r="BB24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC24" t="n">
         <v>12</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>11-10-2008-09</t>
+          <t>2008-11-10</t>
         </is>
       </c>
     </row>
@@ -4847,64 +4914,64 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F25" t="n">
         <v>2</v>
       </c>
       <c r="G25" t="n">
-        <v>0.75</v>
+        <v>0.714</v>
       </c>
       <c r="H25" t="n">
         <v>48</v>
       </c>
       <c r="I25" t="n">
-        <v>36.5</v>
+        <v>36.4</v>
       </c>
       <c r="J25" t="n">
-        <v>70.90000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>0.515</v>
+        <v>0.519</v>
       </c>
       <c r="L25" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="M25" t="n">
-        <v>16.9</v>
+        <v>16.3</v>
       </c>
       <c r="N25" t="n">
-        <v>0.4</v>
+        <v>0.404</v>
       </c>
       <c r="O25" t="n">
-        <v>23.5</v>
+        <v>23.3</v>
       </c>
       <c r="P25" t="n">
-        <v>30.1</v>
+        <v>30.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.78</v>
+        <v>0.765</v>
       </c>
       <c r="R25" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="S25" t="n">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="T25" t="n">
         <v>38.4</v>
       </c>
       <c r="U25" t="n">
-        <v>21.5</v>
+        <v>22.3</v>
       </c>
       <c r="V25" t="n">
-        <v>17.1</v>
+        <v>16.9</v>
       </c>
       <c r="W25" t="n">
-        <v>6.3</v>
+        <v>6.7</v>
       </c>
       <c r="X25" t="n">
         <v>4.9</v>
@@ -4913,13 +4980,13 @@
         <v>3.9</v>
       </c>
       <c r="Z25" t="n">
-        <v>20.3</v>
+        <v>20.1</v>
       </c>
       <c r="AA25" t="n">
         <v>23.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>103.3</v>
+        <v>102.7</v>
       </c>
       <c r="AC25" t="n">
         <v>4.6</v>
@@ -4928,19 +4995,19 @@
         <v>1</v>
       </c>
       <c r="AE25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH25" t="n">
         <v>11</v>
       </c>
       <c r="AI25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ25" t="n">
         <v>30</v>
@@ -4949,13 +5016,13 @@
         <v>1</v>
       </c>
       <c r="AL25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AM25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AN25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO25" t="n">
         <v>3</v>
@@ -4964,7 +5031,7 @@
         <v>4</v>
       </c>
       <c r="AQ25" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AR25" t="n">
         <v>30</v>
@@ -4976,25 +5043,25 @@
         <v>26</v>
       </c>
       <c r="AU25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AV25" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AW25" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AX25" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AY25" t="n">
         <v>5</v>
       </c>
       <c r="AZ25" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA25" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BB25" t="n">
         <v>2</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>11-10-2008-09</t>
+          <t>2008-11-10</t>
         </is>
       </c>
     </row>
@@ -5032,157 +5099,157 @@
         <v>6</v>
       </c>
       <c r="E26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G26" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
       </c>
       <c r="H26" t="n">
         <v>48.8</v>
       </c>
       <c r="I26" t="n">
-        <v>36.2</v>
+        <v>35.2</v>
       </c>
       <c r="J26" t="n">
-        <v>79.7</v>
+        <v>80.3</v>
       </c>
       <c r="K26" t="n">
-        <v>0.454</v>
+        <v>0.438</v>
       </c>
       <c r="L26" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="M26" t="n">
-        <v>19</v>
+        <v>20.2</v>
       </c>
       <c r="N26" t="n">
-        <v>0.412</v>
+        <v>0.397</v>
       </c>
       <c r="O26" t="n">
-        <v>19.2</v>
+        <v>16</v>
       </c>
       <c r="P26" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.799</v>
+        <v>0.762</v>
       </c>
       <c r="R26" t="n">
-        <v>12.3</v>
+        <v>13.7</v>
       </c>
       <c r="S26" t="n">
-        <v>25.5</v>
+        <v>25.8</v>
       </c>
       <c r="T26" t="n">
-        <v>37.8</v>
+        <v>39.5</v>
       </c>
       <c r="U26" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="V26" t="n">
-        <v>10.3</v>
+        <v>11.7</v>
       </c>
       <c r="W26" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="X26" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="Z26" t="n">
-        <v>23.3</v>
+        <v>21.7</v>
       </c>
       <c r="AA26" t="n">
-        <v>20.8</v>
+        <v>19.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>99.3</v>
+        <v>94.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>-0.7</v>
+        <v>-5.2</v>
       </c>
       <c r="AD26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF26" t="n">
         <v>12</v>
       </c>
-      <c r="AE26" t="n">
-        <v>6</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>6</v>
-      </c>
       <c r="AG26" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AH26" t="n">
         <v>4</v>
       </c>
       <c r="AI26" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AJ26" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK26" t="n">
         <v>18</v>
       </c>
-      <c r="AK26" t="n">
-        <v>10</v>
-      </c>
       <c r="AL26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM26" t="n">
         <v>6</v>
       </c>
-      <c r="AM26" t="n">
-        <v>10</v>
-      </c>
       <c r="AN26" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AO26" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="AP26" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AQ26" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="AR26" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AS26" t="n">
         <v>29</v>
       </c>
       <c r="AT26" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AU26" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AV26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW26" t="n">
         <v>19</v>
       </c>
       <c r="AX26" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AY26" t="n">
         <v>1</v>
       </c>
       <c r="AZ26" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>25</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>23</v>
+      </c>
+      <c r="BC26" t="n">
         <v>22</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>22</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>17</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>11-10-2008-09</t>
+          <t>2008-11-10</t>
         </is>
       </c>
     </row>
@@ -5289,16 +5356,16 @@
         <v>-6.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE27" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AF27" t="n">
         <v>18</v>
       </c>
       <c r="AG27" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AH27" t="n">
         <v>11</v>
@@ -5307,7 +5374,7 @@
         <v>1</v>
       </c>
       <c r="AJ27" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AK27" t="n">
         <v>3</v>
@@ -5319,13 +5386,13 @@
         <v>19</v>
       </c>
       <c r="AN27" t="n">
+        <v>19</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>17</v>
+      </c>
+      <c r="AP27" t="n">
         <v>20</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>18</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>22</v>
       </c>
       <c r="AQ27" t="n">
         <v>3</v>
@@ -5334,16 +5401,16 @@
         <v>27</v>
       </c>
       <c r="AS27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT27" t="n">
+        <v>26</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>16</v>
+      </c>
+      <c r="AV27" t="n">
         <v>25</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>15</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>27</v>
       </c>
       <c r="AW27" t="n">
         <v>26</v>
@@ -5355,13 +5422,13 @@
         <v>13</v>
       </c>
       <c r="AZ27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA27" t="n">
         <v>20</v>
       </c>
       <c r="BB27" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BC27" t="n">
         <v>25</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>11-10-2008-09</t>
+          <t>2008-11-10</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>-7</v>
       </c>
       <c r="AD28" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE28" t="n">
         <v>26</v>
@@ -5492,10 +5559,10 @@
         <v>16</v>
       </c>
       <c r="AK28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AM28" t="n">
         <v>7</v>
@@ -5510,22 +5577,22 @@
         <v>30</v>
       </c>
       <c r="AQ28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR28" t="n">
         <v>28</v>
       </c>
       <c r="AS28" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>24</v>
+      </c>
+      <c r="AU28" t="n">
         <v>15</v>
       </c>
-      <c r="AT28" t="n">
-        <v>22</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>14</v>
-      </c>
       <c r="AV28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW28" t="n">
         <v>30</v>
@@ -5537,13 +5604,13 @@
         <v>12</v>
       </c>
       <c r="AZ28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA28" t="n">
         <v>30</v>
       </c>
       <c r="BB28" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC28" t="n">
         <v>26</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>11-10-2008-09</t>
+          <t>2008-11-10</t>
         </is>
       </c>
     </row>
@@ -5575,121 +5642,121 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E29" t="n">
         <v>4</v>
       </c>
       <c r="F29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G29" t="n">
-        <v>0.571</v>
+        <v>0.667</v>
       </c>
       <c r="H29" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="I29" t="n">
-        <v>34.7</v>
+        <v>35</v>
       </c>
       <c r="J29" t="n">
-        <v>75.09999999999999</v>
+        <v>74.8</v>
       </c>
       <c r="K29" t="n">
-        <v>0.462</v>
+        <v>0.468</v>
       </c>
       <c r="L29" t="n">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="M29" t="n">
-        <v>14.9</v>
+        <v>14.2</v>
       </c>
       <c r="N29" t="n">
-        <v>0.442</v>
+        <v>0.447</v>
       </c>
       <c r="O29" t="n">
-        <v>18.1</v>
+        <v>19</v>
       </c>
       <c r="P29" t="n">
-        <v>22</v>
+        <v>22.7</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.825</v>
+        <v>0.838</v>
       </c>
       <c r="R29" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="S29" t="n">
-        <v>30</v>
+        <v>29.8</v>
       </c>
       <c r="T29" t="n">
-        <v>36.7</v>
+        <v>36.3</v>
       </c>
       <c r="U29" t="n">
-        <v>24</v>
+        <v>23.8</v>
       </c>
       <c r="V29" t="n">
-        <v>13.4</v>
+        <v>13</v>
       </c>
       <c r="W29" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="X29" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>95.3</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF29" t="n">
         <v>5</v>
       </c>
-      <c r="X29" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>94.09999999999999</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>6</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>11</v>
-      </c>
       <c r="AG29" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AH29" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AI29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ29" t="n">
         <v>28</v>
       </c>
       <c r="AK29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AL29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AM29" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AN29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO29" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AP29" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AQ29" t="n">
         <v>2</v>
@@ -5698,7 +5765,7 @@
         <v>29</v>
       </c>
       <c r="AS29" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AT29" t="n">
         <v>30</v>
@@ -5707,28 +5774,28 @@
         <v>2</v>
       </c>
       <c r="AV29" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AW29" t="n">
         <v>29</v>
       </c>
       <c r="AX29" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="AY29" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AZ29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BA29" t="n">
+        <v>22</v>
+      </c>
+      <c r="BB29" t="n">
         <v>21</v>
       </c>
-      <c r="BB29" t="n">
-        <v>22</v>
-      </c>
       <c r="BC29" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>11-10-2008-09</t>
+          <t>2008-11-10</t>
         </is>
       </c>
     </row>
@@ -5835,10 +5902,10 @@
         <v>8</v>
       </c>
       <c r="AD30" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF30" t="n">
         <v>3</v>
@@ -5853,7 +5920,7 @@
         <v>3</v>
       </c>
       <c r="AJ30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK30" t="n">
         <v>2</v>
@@ -5865,52 +5932,52 @@
         <v>29</v>
       </c>
       <c r="AN30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO30" t="n">
         <v>13</v>
       </c>
       <c r="AP30" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ30" t="n">
         <v>12</v>
       </c>
-      <c r="AQ30" t="n">
-        <v>15</v>
-      </c>
       <c r="AR30" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AS30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AT30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU30" t="n">
         <v>1</v>
       </c>
       <c r="AV30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX30" t="n">
         <v>25</v>
       </c>
       <c r="AY30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ30" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB30" t="n">
         <v>11</v>
       </c>
-      <c r="BA30" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>12</v>
-      </c>
       <c r="BC30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>11-10-2008-09</t>
+          <t>2008-11-10</t>
         </is>
       </c>
     </row>
@@ -6017,13 +6084,13 @@
         <v>-11.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE31" t="n">
         <v>30</v>
       </c>
       <c r="AF31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG31" t="n">
         <v>30</v>
@@ -6032,10 +6099,10 @@
         <v>3</v>
       </c>
       <c r="AI31" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AJ31" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AK31" t="n">
         <v>13</v>
@@ -6044,7 +6111,7 @@
         <v>25</v>
       </c>
       <c r="AM31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AN31" t="n">
         <v>30</v>
@@ -6056,22 +6123,22 @@
         <v>7</v>
       </c>
       <c r="AQ31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AR31" t="n">
         <v>26</v>
       </c>
       <c r="AS31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT31" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AU31" t="n">
         <v>19</v>
       </c>
       <c r="AV31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW31" t="n">
         <v>21</v>
@@ -6086,10 +6153,10 @@
         <v>16</v>
       </c>
       <c r="BA31" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="BB31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BC31" t="n">
         <v>29</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>11-10-2008-09</t>
+          <t>2008-11-10</t>
         </is>
       </c>
     </row>
